--- a/output/pdf_financials_xlsx/SOLI.P.xlsx
+++ b/output/pdf_financials_xlsx/SOLI.P.xlsx
@@ -2503,16 +2503,16 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.06472899999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.06472899999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.06472899999999999</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.06472899999999999</v>
       </c>
     </row>
     <row r="93">
@@ -3862,7 +3862,11 @@
           <t>Reserve 4</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -4147,7 +4151,11 @@
           <t>Reserve 3</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SOLI.P.xlsx
+++ b/output/pdf_financials_xlsx/SOLI.P.xlsx
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.004454</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.000349</v>
+        <v>0.180427</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.000284</v>
+        <v>0.060747</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.000288</v>
+        <v>0.051327</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.00028</v>
+        <v>0.068075</v>
       </c>
     </row>
     <row r="11">
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.004454</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.000349</v>
+        <v>-0.180427</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.000284</v>
+        <v>-0.060747</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.000288</v>
+        <v>-0.051327</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.00028</v>
+        <v>-0.068075</v>
       </c>
     </row>
     <row r="12">
@@ -675,13 +675,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000671</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005895</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00682</v>
       </c>
     </row>
     <row r="13">
@@ -1031,13 +1031,13 @@
         <v>-0.180427</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.060747</v>
+        <v>-0.060076</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.051327</v>
+        <v>-0.045432</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.068075</v>
+        <v>-0.061255</v>
       </c>
     </row>
     <row r="28">
@@ -1075,13 +1075,13 @@
         <v>-0.180427</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.060747</v>
+        <v>-0.060076</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.051327</v>
+        <v>-0.045432</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.068075</v>
+        <v>-0.061255</v>
       </c>
     </row>
     <row r="30">
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.280134</v>
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.280134</v>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
